--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="R249221f339854318"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="Rdbfdb02223114c1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>input_data/training_requests.csv、team_controls.csv、pool_plan.csv、rehearsal_scenarios.csv、release_policy.json、starter/shared_gpu_release_rehearsal_starter.py和数据说明.md</x:v>
+        <x:v>input_data/training_requests.csv、team_controls.csv、pool_plan.csv、rehearsal_scenarios.csv、release_policy.json、report_contract.csv、starter/shared_gpu_release_rehearsal_starter.py和数据说明.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -341,7 +341,7 @@
         <x:v>目标输出文件</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>dags和tools目录各一份Python文件，reports目录五份CSV，以及runtime_events目录中的场景事件</x:v>
+        <x:v>dags和tools目录各一份Python文件，reports目录五份CSV</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -349,7 +349,7 @@
         <x:v>核心操作链</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>关联申请与团队控制→校验Pool及槽位→写入Airflow Pool→完成DAG结构→DagBag导入→运行两个场景→回读DagRun和TaskInstance→汇总租约事件</x:v>
+        <x:v>关联申请与团队控制→校验Pool及槽位→写入Airflow Pool→完成DAG结构→DagBag导入→运行两个场景→回读DagRun和TaskInstance→按报告合同汇总租约事件</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -357,7 +357,7 @@
         <x:v>输入一致性模块</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>业务主键唯一，团队和Pool外键存在，申请Pool符合团队权限，pool_slots不超过团队上限，失败对象属于申请集合</x:v>
+        <x:v>业务主键唯一，团队和Pool外键存在，申请Pool符合团队权限，pool_slots不超过团队上限，失败对象属于申请集合，报告合同路径与字段完整</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -381,7 +381,7 @@
         <x:v>任务资源模块</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>五个申请任务按release_order连接，pool和pool_slots逐行来自training_requests.csv</x:v>
+        <x:v>五个任务组标识逐行来自training_requests.csv，组内任务标识来自release_policy.json，申请任务按release_order连接，pool和pool_slots来自申请表</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -405,7 +405,7 @@
         <x:v>状态导出模块</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>从本次元数据库和DAG对象导出结构、Pool、场景、TaskInstance和事件报告，不用预期状态代替观测状态</x:v>
+        <x:v>按report_contract.csv从本次元数据库和DAG对象导出结构、Pool、场景、TaskInstance和事件报告，不用预期状态代替观测状态</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -413,7 +413,7 @@
         <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>七项文件路径与runtime_events齐全，DAG可导入，两个场景状态符合输入，两个场景各释放一次租约，报告可反向连接本次Airflow对象</x:v>
+        <x:v>七项文件路径齐全且没有未列明目录，DAG可导入，两个场景状态符合输入，两个场景各释放一次租约，报告可反向连接本次Airflow对象</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">

--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="Rdbfdb02223114c1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="R126576f33f214eca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -362,73 +362,81 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
-        <x:v>Airflow Pool模块</x:v>
+        <x:v>运行入口模块</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>按pool_plan.csv创建或更新gpu_standard和gpu_memory，并从本次元数据库回读slots、include_deferred和description</x:v>
+        <x:v>tools/run_rehearsal.py接受input、output和dag-file三个参数，有效输入生成交付，输入错误或目标已存在时失败关闭</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>DAG装载模块</x:v>
+        <x:v>Airflow Pool模块</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>DagBag只装载最终dags目录，import_errors为空，DAG边界取自release_policy.json</x:v>
+        <x:v>按pool_plan.csv创建或更新gpu_standard和gpu_memory，并从本次元数据库回读slots、include_deferred和description</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
-        <x:v>任务资源模块</x:v>
+        <x:v>DAG装载模块</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>五个任务组标识逐行来自training_requests.csv，组内任务标识来自release_policy.json，申请任务按release_order连接，pool和pool_slots来自申请表</x:v>
+        <x:v>DagBag只装载最终dags目录，import_errors为空，DAG边界取自release_policy.json</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="str">
-        <x:v>租约生命周期模块</x:v>
+        <x:v>任务资源模块</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>acquire_release_lease标记为setup，release_release_lease标记为teardown并关联setup，释放后保留失败DagRun</x:v>
+        <x:v>五个任务组标识逐行来自training_requests.csv，组内任务标识来自release_policy.json，申请任务按release_order连接，pool和pool_slots来自申请表</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="str">
-        <x:v>场景运行模块</x:v>
+        <x:v>租约生命周期模块</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>按rehearsal_scenarios.csv的逻辑日期运行release_ready和verification_stop，实际生成DagRun与TaskInstance</x:v>
+        <x:v>acquire_release_lease标记为setup，release_release_lease标记为teardown并关联setup，释放后保留失败DagRun</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>状态导出模块</x:v>
+        <x:v>场景运行模块</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>按report_contract.csv从本次元数据库和DAG对象导出结构、Pool、场景、TaskInstance和事件报告，不用预期状态代替观测状态</x:v>
+        <x:v>按rehearsal_scenarios.csv的逻辑日期运行release_ready和verification_stop，实际生成DagRun与TaskInstance</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>状态导出模块</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>七项文件路径齐全且没有未列明目录，DAG可导入，两个场景状态符合输入，两个场景各释放一次租约，报告可反向连接本次Airflow对象</x:v>
+        <x:v>按report_contract.csv从本次元数据库和DAG对象导出结构、Pool、场景、TaskInstance和事件报告，事件detail原样使用申请表和发布策略中的对应值，不用预期状态代替观测状态</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="str">
+        <x:v>完成条件</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="str">
+        <x:v>七项文件路径齐全且没有未列明目录，DAG可导入，两个场景状态符合输入，两个场景各释放一次租约，报告可反向连接本次Airflow对象</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="5" t="str">
         <x:v>可验证点</x:v>
       </x:c>
-      <x:c r="B18" s="5" t="str">
+      <x:c r="B19" s="5" t="str">
         <x:v>主键与外键、Pool容量、任务集合、依赖链、setup与teardown、trigger_rule、DagRun状态、TaskInstance状态、事件集合和跨报告一致性</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="6" t="str">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="6" t="str">
         <x:v>不适合作为评分点的内容</x:v>
       </x:c>
-      <x:c r="B19" s="6" t="str">
+      <x:c r="B20" s="6" t="str">
         <x:v>Python缩进风格、函数拆分、变量名、CSV行序、日志时间、编辑器选择和表格配色</x:v>
       </x:c>
     </x:row>

--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="R126576f33f214eca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="R1d0823ab937c44c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -317,7 +317,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>训练平台发布值班提供的自造演练材料</x:v>
+        <x:v>训练平台发布值班提供的共享GPU窗口申请、资源池方案和发布策略</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
